--- a/asc/sc_scasc/003_325423/条件输入数据表.xlsx
+++ b/asc/sc_scasc/003_325423/条件输入数据表.xlsx
@@ -1173,8 +1173,16 @@
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr"/>
-      <c r="D3" s="33" t="inlineStr"/>
-      <c r="E3" s="17" t="inlineStr"/>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>轻度</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>轻度</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>设计压力*</t>
@@ -1297,8 +1305,16 @@
           <t>MPa</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>工作温度（出口）</t>
@@ -1409,8 +1425,16 @@
           <t>℃</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr"/>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="28" t="inlineStr">
@@ -1428,8 +1452,16 @@
           <t>℃</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="inlineStr">
@@ -1447,8 +1479,16 @@
           <t>℃</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="28" t="inlineStr">
@@ -1485,8 +1525,16 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr"/>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="28" t="inlineStr">
@@ -1846,9 +1894,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
